--- a/datos/06-analisis-desviaciones-rendimientos.xlsx
+++ b/datos/06-analisis-desviaciones-rendimientos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1009" documentId="8_{566A70F3-096B-4476-B336-90A9B7DB3344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0036DA0-24B5-45D8-86D0-D85536EC5F8F}"/>
+  <xr:revisionPtr revIDLastSave="1058" documentId="8_{566A70F3-096B-4476-B336-90A9B7DB3344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2BFDFA9-E840-4E2F-9715-FDC53E678BFF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="675" activeTab="3" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
   </bookViews>

--- a/datos/06-analisis-desviaciones-rendimientos.xlsx
+++ b/datos/06-analisis-desviaciones-rendimientos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1058" documentId="8_{566A70F3-096B-4476-B336-90A9B7DB3344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2BFDFA9-E840-4E2F-9715-FDC53E678BFF}"/>
+  <xr:revisionPtr revIDLastSave="1087" documentId="8_{566A70F3-096B-4476-B336-90A9B7DB3344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8731966B-7E41-48BD-828D-BD5FD931E4DA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="675" activeTab="3" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
   </bookViews>
@@ -870,12 +870,6 @@
     <t>Otros efectos no explicados</t>
   </si>
   <si>
-    <t>MP leche cuba</t>
-  </si>
-  <si>
-    <t>MG leche cuba</t>
-  </si>
-  <si>
     <t>Coste de la leche en fabrica</t>
   </si>
   <si>
@@ -1090,6 +1084,12 @@
   </si>
   <si>
     <t xml:space="preserve">Recup MP </t>
+  </si>
+  <si>
+    <t>MG leche cuba (kg)</t>
+  </si>
+  <si>
+    <t>MP leche cuba (kg)</t>
   </si>
 </sst>
 </file>
@@ -3928,10 +3928,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="117" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B2" s="118" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C2" s="118" t="s">
         <v>4</v>
@@ -3939,7 +3939,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="55" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B3" s="104">
         <v>0.51</v>
@@ -3950,7 +3950,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B4" s="105">
         <v>2.7E-2</v>
@@ -3961,7 +3961,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B5" s="105">
         <v>1.4999999999999999E-2</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="37" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B6" s="106">
         <v>1.4999999999999999E-2</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="55" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B7" s="104">
         <f>SUM(B3:B6)</f>
@@ -3996,7 +3996,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B8" s="119">
         <v>2.1000000000000001E-2</v>
@@ -4007,7 +4007,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="103" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9" s="124">
         <f>SUM(B7:B8)</f>
@@ -4020,7 +4020,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B10" s="105">
         <f>B27*B16/1000</f>
@@ -4033,7 +4033,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B11" s="106">
         <f>B28*B17/1000</f>
@@ -4046,14 +4046,14 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="62" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B13" s="107">
         <v>4.1000000000000002E-2</v>
@@ -4064,7 +4064,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="40" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B14" s="20">
         <v>3.4500000000000003E-2</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B16" s="12">
         <f>B13*B21*1000</f>
@@ -4095,7 +4095,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B17" s="12">
         <f>B14*B21*1000</f>
@@ -4108,7 +4108,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B18" s="12">
         <v>48</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="23" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B19" s="12">
         <v>9</v>
@@ -4130,7 +4130,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B20" s="12">
         <f>B21*1000-SUM(B16:B19)</f>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B21" s="12">
         <f>(-0.2307*10^(-2)*B22^2-0.2655*B22+1040.51-B13*(-0.478*10^(-4)*B22^2+0.969*10^(-2)*B22+0.967))/1000</f>
@@ -4156,7 +4156,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B22" s="68">
         <v>20</v>
@@ -4167,14 +4167,14 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="66" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="36" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B24" s="120">
         <v>0.4</v>
@@ -4186,7 +4186,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="36" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B25" s="67">
         <f>1-B24</f>
@@ -4200,7 +4200,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="123" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -4208,7 +4208,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="36" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B27" s="121">
         <f>B9/B16*B24*1000</f>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="37" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B28" s="122">
         <f>B9/B17*B25*1000</f>
@@ -4277,10 +4277,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B1" s="69" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -4293,13 +4293,13 @@
     </row>
     <row r="3" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="131" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B3" s="59"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B4" s="26">
         <v>0.52</v>
@@ -4307,7 +4307,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="40" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B5" s="38">
         <v>0.27</v>
@@ -4342,13 +4342,13 @@
     </row>
     <row r="9" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="131" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B9" s="129"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B10" s="59">
         <v>40.35</v>
@@ -4356,7 +4356,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="40" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B11" s="44">
         <v>34.11</v>
@@ -4364,13 +4364,13 @@
     </row>
     <row r="12" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="131" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B12" s="130"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="40" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B13" s="38">
         <v>0.92</v>
@@ -4378,13 +4378,13 @@
     </row>
     <row r="14" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="71" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B14" s="72"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B15" s="31">
         <f>B13*B11</f>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="75" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B19" s="76">
         <f>B17-B10</f>
@@ -4429,7 +4429,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B20" s="77">
         <f>B19/B10</f>
@@ -4438,7 +4438,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="75" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B21" s="9">
         <f>B10*B16</f>
@@ -4470,12 +4470,12 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="35" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B2" s="133">
         <v>45292</v>
@@ -4499,7 +4499,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B5" s="38">
         <v>0.25459999999999999</v>
@@ -4515,7 +4515,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B7" s="59">
         <v>41.07</v>
@@ -4523,7 +4523,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B8" s="44">
         <v>33.950000000000003</v>
@@ -4549,7 +4549,7 @@
     </row>
     <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="41" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B11" s="17"/>
     </row>
@@ -4563,7 +4563,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="42" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B13" s="64">
         <v>0.4</v>
@@ -4571,7 +4571,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="42" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B14" s="54">
         <f>B13/100*B16*1000*100</f>
@@ -4580,7 +4580,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B15" s="39">
         <v>5.91</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="43" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B16" s="56">
         <v>0.98499999999999999</v>
@@ -4654,15 +4654,16 @@
     <col min="1" max="1" width="49.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="12.42578125" customWidth="1"/>
     <col min="4" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="6" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C1" s="18" t="s">
         <v>4</v>
@@ -4800,7 +4801,6 @@
         <f>'Datos fabricación real'!B6</f>
         <v>5025</v>
       </c>
-      <c r="E11" s="33"/>
       <c r="F11" s="22"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -4815,6 +4815,7 @@
         <f>C14/C11*1000</f>
         <v>41.069999999999993</v>
       </c>
+      <c r="E12" s="32"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
@@ -5044,7 +5045,7 @@
     </row>
     <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="109" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B30" s="110" t="s">
         <v>40</v>
@@ -5053,20 +5054,20 @@
         <v>4</v>
       </c>
       <c r="D30" s="111" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E30" s="108" t="s">
+        <v>91</v>
+      </c>
+      <c r="F30" s="108" t="s">
         <v>93</v>
-      </c>
-      <c r="F30" s="108" t="s">
-        <v>95</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="75" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B31" s="9">
         <f>B14/C2*1000</f>
@@ -5093,7 +5094,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="40" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B32" s="7">
         <f>B15/C2*1000</f>
@@ -5120,7 +5121,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="63" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B33" s="53"/>
       <c r="C33" s="24"/>
@@ -5138,7 +5139,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="75" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B34" s="125">
         <v>5.5469999999999997</v>
@@ -5160,7 +5161,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B35" s="126">
         <v>9.8879999999999999</v>
@@ -5182,7 +5183,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="103" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
@@ -5209,7 +5210,7 @@
     </row>
     <row r="38" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="113" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B38" s="114" t="s">
         <v>40</v>
@@ -5221,17 +5222,17 @@
         <v>41</v>
       </c>
       <c r="E38" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="F38" s="108" t="s">
         <v>93</v>
-      </c>
-      <c r="F38" s="108" t="s">
-        <v>95</v>
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="B39" s="15">
         <f>B14</f>
@@ -5258,7 +5259,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="82" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="B40" s="21">
         <f>B15</f>
@@ -5300,7 +5301,7 @@
     </row>
     <row r="43" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="112" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B43" s="51" t="s">
         <v>40</v>
@@ -5309,13 +5310,13 @@
         <v>4</v>
       </c>
       <c r="D43" s="51" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E43" s="108" t="s">
+        <v>91</v>
+      </c>
+      <c r="F43" s="115" t="s">
         <v>93</v>
-      </c>
-      <c r="F43" s="115" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -5399,7 +5400,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="84" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B48" s="86"/>
       <c r="C48" s="86"/>
@@ -5497,7 +5498,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="90" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B53" s="21"/>
       <c r="C53" s="88"/>
@@ -5548,7 +5549,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E56" s="15">
         <f>SUM(E46,E51)</f>
@@ -5575,7 +5576,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="94" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B58" s="95"/>
       <c r="C58" s="95"/>

--- a/datos/06-analisis-desviaciones-rendimientos.xlsx
+++ b/datos/06-analisis-desviaciones-rendimientos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1087" documentId="8_{566A70F3-096B-4476-B336-90A9B7DB3344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8731966B-7E41-48BD-828D-BD5FD931E4DA}"/>
+  <xr:revisionPtr revIDLastSave="1107" documentId="8_{566A70F3-096B-4476-B336-90A9B7DB3344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24FA3876-6587-4C44-82C4-DD70C2D64224}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="675" activeTab="3" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
+    <workbookView xWindow="2820" yWindow="540" windowWidth="23595" windowHeight="14250" tabRatio="675" activeTab="3" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos materia prima" sheetId="8" r:id="rId1"/>
@@ -1168,12 +1168,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1206,6 +1200,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -1381,7 +1381,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1408,9 +1408,6 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1422,13 +1419,13 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1442,8 +1439,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -1456,7 +1453,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1467,7 +1464,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1478,8 +1475,8 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1488,7 +1485,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="4"/>
     </xf>
@@ -1503,12 +1500,12 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -1548,8 +1545,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1558,35 +1555,35 @@
     <xf numFmtId="170" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1597,17 +1594,25 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="170" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares 2" xfId="2" xr:uid="{0DF497A4-B1A4-4A8E-B2C1-3A725AAFDCC2}"/>
@@ -1632,6 +1637,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="RDT (2)"/>
       <sheetName val="VERIF"/>
@@ -3456,6 +3464,9 @@
 <file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="SYNT"/>
       <sheetName val="PE"/>
@@ -3610,10 +3621,6 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3922,166 +3929,166 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="34" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="117" t="s">
+      <c r="A2" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="118" t="s">
+      <c r="B2" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="118" t="s">
+      <c r="C2" s="117" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="B3" s="104">
+      <c r="B3" s="103">
         <v>0.51</v>
       </c>
-      <c r="C3" s="104">
+      <c r="C3" s="103">
         <v>0.51</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="105">
+      <c r="B4" s="104">
         <v>2.7E-2</v>
       </c>
-      <c r="C4" s="105">
+      <c r="C4" s="104">
         <v>1.5500000000000014E-2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="105">
+      <c r="B5" s="104">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C5" s="105">
+      <c r="C5" s="104">
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="106">
+      <c r="B6" s="105">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C6" s="106">
+      <c r="C6" s="105">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="B7" s="104">
+      <c r="B7" s="103">
         <f>SUM(B3:B6)</f>
         <v>0.56700000000000006</v>
       </c>
-      <c r="C7" s="104">
+      <c r="C7" s="103">
         <f>SUM(C3:C6)</f>
         <v>0.5475000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="B8" s="119">
+      <c r="B8" s="118">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="C8" s="119">
+      <c r="C8" s="118">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="103" t="s">
+      <c r="A9" s="102" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="124">
+      <c r="B9" s="123">
         <f>SUM(B7:B8)</f>
         <v>0.58800000000000008</v>
       </c>
-      <c r="C9" s="124">
+      <c r="C9" s="123">
         <f>SUM(C7:C8)</f>
         <v>0.57250000000000012</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="B10" s="105">
+      <c r="B10" s="104">
         <f>B27*B16/1000</f>
         <v>0.23520000000000005</v>
       </c>
-      <c r="C10" s="105">
+      <c r="C10" s="104">
         <f>C27*C16/1000</f>
         <v>0.22900000000000006</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="106">
+      <c r="B11" s="105">
         <f>B28*B17/1000</f>
         <v>0.35280000000000006</v>
       </c>
-      <c r="C11" s="106">
+      <c r="C11" s="105">
         <f>C28*C17/1000</f>
         <v>0.34350000000000008</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="62" t="s">
+      <c r="A12" s="61" t="s">
         <v>48</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="107">
+      <c r="B13" s="106">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="C13" s="107">
+      <c r="C13" s="106">
         <v>3.95E-2</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="19">
         <v>3.4500000000000003E-2</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="19">
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="63" t="s">
+      <c r="A15" s="62" t="s">
         <v>37</v>
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
         <v>104</v>
       </c>
       <c r="B16" s="12">
@@ -4094,7 +4101,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="22" t="s">
         <v>105</v>
       </c>
       <c r="B17" s="12">
@@ -4107,7 +4114,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="22" t="s">
         <v>106</v>
       </c>
       <c r="B18" s="12">
@@ -4118,7 +4125,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="22" t="s">
         <v>107</v>
       </c>
       <c r="B19" s="12">
@@ -4129,7 +4136,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="22" t="s">
         <v>108</v>
       </c>
       <c r="B20" s="12">
@@ -4142,7 +4149,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="22" t="s">
         <v>109</v>
       </c>
       <c r="B21" s="12">
@@ -4155,108 +4162,108 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="65" t="s">
+      <c r="A22" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="68">
+      <c r="B22" s="67">
         <v>20</v>
       </c>
-      <c r="C22" s="68">
+      <c r="C22" s="67">
         <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="66" t="s">
+      <c r="A23" s="65" t="s">
         <v>52</v>
       </c>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="36" t="s">
+      <c r="A24" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="B24" s="120">
+      <c r="B24" s="119">
         <v>0.4</v>
       </c>
-      <c r="C24" s="120">
+      <c r="C24" s="119">
         <v>0.4</v>
       </c>
-      <c r="D24" s="52"/>
+      <c r="D24" s="51"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="B25" s="67">
+      <c r="B25" s="66">
         <f>1-B24</f>
         <v>0.6</v>
       </c>
-      <c r="C25" s="67">
+      <c r="C25" s="66">
         <f>1-C24</f>
         <v>0.6</v>
       </c>
-      <c r="D25" s="52"/>
+      <c r="D25" s="51"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="123" t="s">
+      <c r="A26" s="122" t="s">
         <v>72</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
-      <c r="D26" s="52"/>
+      <c r="D26" s="51"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="36" t="s">
+      <c r="A27" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="B27" s="121">
+      <c r="B27" s="120">
         <f>B9/B16*B24*1000</f>
         <v>5.5467190048837516</v>
       </c>
-      <c r="C27" s="121">
+      <c r="C27" s="120">
         <f>C9/C16*C24*1000</f>
         <v>5.6055776397059009</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="37" t="s">
+      <c r="A28" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="B28" s="122">
+      <c r="B28" s="121">
         <f>B9/B17*B25*1000</f>
         <v>9.8876295304449471</v>
       </c>
-      <c r="C28" s="122">
+      <c r="C28" s="121">
         <f>C9/C17*C25*1000</f>
         <v>9.7685433868404292</v>
       </c>
-      <c r="D28" s="52"/>
+      <c r="D28" s="51"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D29" s="52"/>
+      <c r="D29" s="51"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D30" s="52"/>
+      <c r="D30" s="51"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="52"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D33" s="52"/>
+      <c r="D33" s="51"/>
     </row>
     <row r="34" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D34" s="52"/>
+      <c r="D34" s="51"/>
     </row>
     <row r="35" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D35" s="52"/>
+      <c r="D35" s="51"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4276,45 +4283,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="68" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="132">
+      <c r="B2" s="131">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="131" t="s">
+      <c r="A3" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="59"/>
+      <c r="B3" s="58"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="25">
         <v>0.52</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="37">
         <v>0.27</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="22" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="11">
@@ -4323,7 +4330,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="16">
@@ -4332,112 +4339,112 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="19">
         <f>B5/B4</f>
         <v>0.51923076923076927</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A9" s="131" t="s">
+      <c r="A9" s="130" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="129"/>
+      <c r="B9" s="128"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="59">
+      <c r="B10" s="58">
         <v>40.35</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="44">
+      <c r="B11" s="43">
         <v>34.11</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A12" s="131" t="s">
+      <c r="A12" s="130" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="130"/>
+      <c r="B12" s="129"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="B13" s="38">
+      <c r="B13" s="37">
         <v>0.92</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A14" s="71" t="s">
+      <c r="A14" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="72"/>
+      <c r="B14" s="71"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="30">
         <f>B13*B11</f>
         <v>31.3812</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="73">
+      <c r="B16" s="72">
         <f>B6*1000/B15</f>
         <v>7.9665532229487717</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="30">
         <f>B5*1000/B16</f>
         <v>33.891696000000003</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="74">
+      <c r="B18" s="73">
         <f>B17/B10</f>
         <v>0.83994289962825286</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="75" t="s">
+      <c r="A19" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="76">
+      <c r="B19" s="75">
         <f>B17-B10</f>
         <v>-6.4583039999999983</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="B20" s="77">
+      <c r="B20" s="76">
         <f>B19/B10</f>
         <v>-0.16005710037174717</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="75" t="s">
+      <c r="A21" s="74" t="s">
         <v>66</v>
       </c>
       <c r="B21" s="9">
@@ -4446,7 +4453,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="39" t="s">
         <v>5</v>
       </c>
       <c r="B22" s="7">
@@ -4469,68 +4476,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="133" t="s">
         <v>47</v>
       </c>
+      <c r="B1" s="134"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="133">
+      <c r="B2" s="132">
         <v>45292</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="58">
+      <c r="B3" s="57">
         <v>637.55999999999995</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="25">
         <v>0.4995</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="37">
         <v>0.25459999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="29">
         <v>5025</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="59">
+      <c r="B7" s="58">
         <v>41.07</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="44">
+      <c r="B8" s="43">
         <v>33.950000000000003</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="35" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="15">
@@ -4539,7 +4547,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="35" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="15">
@@ -4548,95 +4556,95 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="40" t="s">
         <v>71</v>
       </c>
       <c r="B11" s="17"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="59">
+      <c r="B12" s="58">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="64">
+      <c r="B13" s="63">
         <v>0.4</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="54">
+      <c r="B14" s="53">
         <f>B13/100*B16*1000*100</f>
         <v>394</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="42" t="s">
+      <c r="A15" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="39">
+      <c r="B15" s="38">
         <v>5.91</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="56">
+      <c r="B16" s="55">
         <v>0.98499999999999999</v>
       </c>
     </row>
     <row r="18" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C18" s="33"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C19" s="33"/>
+      <c r="C19" s="32"/>
     </row>
     <row r="24" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="E24" s="24"/>
-      <c r="F24" s="52"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="51"/>
     </row>
     <row r="25" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="E25" s="24"/>
-      <c r="F25" s="52"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="51"/>
     </row>
     <row r="26" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="F26" s="52"/>
+      <c r="F26" s="51"/>
     </row>
     <row r="28" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="E28" s="24"/>
-      <c r="F28" s="52"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="51"/>
     </row>
     <row r="29" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="E29" s="24"/>
-      <c r="F29" s="52"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="51"/>
     </row>
     <row r="30" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="E30" s="24"/>
-      <c r="F30" s="52"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="51"/>
     </row>
     <row r="31" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="F31" s="52"/>
+      <c r="F31" s="51"/>
     </row>
     <row r="32" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="F32" s="52"/>
+      <c r="F32" s="51"/>
     </row>
     <row r="33" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F33" s="52"/>
+      <c r="F33" s="51"/>
     </row>
     <row r="34" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F34" s="52"/>
+      <c r="F34" s="51"/>
     </row>
     <row r="35" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F35" s="52"/>
+      <c r="F35" s="51"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4659,13 +4667,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="135" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="136" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="136" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4673,8 +4681,8 @@
       <c r="A2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="60">
+      <c r="B2" s="69"/>
+      <c r="C2" s="59">
         <f>'Datos fabricación real'!B3</f>
         <v>637.55999999999995</v>
       </c>
@@ -4687,27 +4695,27 @@
         <f>'Estándar técnico'!B4</f>
         <v>0.52</v>
       </c>
-      <c r="C3" s="46">
+      <c r="C3" s="45">
         <f>'Datos fabricación real'!B4</f>
         <v>0.4995</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="11">
         <f>'Estándar técnico'!B5</f>
         <v>0.27</v>
       </c>
-      <c r="C4" s="47">
+      <c r="C4" s="46">
         <f>'Datos fabricación real'!B5</f>
         <v>0.25459999999999999</v>
       </c>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="22" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="11">
@@ -4737,11 +4745,11 @@
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="19">
         <f>B4/B3</f>
         <v>0.51923076923076927</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="19">
         <f>C4/C3</f>
         <v>0.50970970970970975</v>
       </c>
@@ -4786,7 +4794,7 @@
         <f>C8/C9</f>
         <v>1.0396080032666395</v>
       </c>
-      <c r="E10" s="48"/>
+      <c r="E10" s="47"/>
       <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -4797,35 +4805,35 @@
         <f>B15/B19*1000</f>
         <v>5079.155672823219</v>
       </c>
-      <c r="C11" s="45">
+      <c r="C11" s="44">
         <f>'Datos fabricación real'!B6</f>
         <v>5025</v>
       </c>
-      <c r="F11" s="22"/>
+      <c r="F11" s="21"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="30">
         <f>'Estándar técnico'!B10</f>
         <v>40.35</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="30">
         <f>C14/C11*1000</f>
         <v>41.069999999999993</v>
       </c>
-      <c r="E12" s="32"/>
+      <c r="E12" s="31"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="30">
         <f>'Estándar técnico'!B11</f>
         <v>34.11</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="30">
         <f>C15/C11*1000</f>
         <v>33.950000000000003</v>
       </c>
@@ -4835,11 +4843,11 @@
       <c r="A14" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="30">
         <f>B$4/B$22*C$2</f>
         <v>204.94393139841688</v>
       </c>
-      <c r="C14" s="61">
+      <c r="C14" s="60">
         <f>'Datos fabricación real'!B9</f>
         <v>206.37674999999999</v>
       </c>
@@ -4849,11 +4857,11 @@
       <c r="A15" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="30">
         <f>C$2*B$5/B$23</f>
         <v>173.24999999999997</v>
       </c>
-      <c r="C15" s="61">
+      <c r="C15" s="60">
         <f>'Datos fabricación real'!B10</f>
         <v>170.59875</v>
       </c>
@@ -4864,26 +4872,26 @@
       <c r="A16" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="30">
         <f>B11*B26/1000</f>
         <v>0</v>
       </c>
-      <c r="C16" s="61">
+      <c r="C16" s="60">
         <f>'Datos fabricación real'!B12</f>
         <v>0</v>
       </c>
-      <c r="D16" s="29"/>
-      <c r="H16" s="24"/>
+      <c r="D16" s="28"/>
+      <c r="H16" s="23"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="20">
         <f>B14/B15</f>
         <v>1.1829375549692174</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="20">
         <f>C14/C15</f>
         <v>1.2097201767304859</v>
       </c>
@@ -4900,7 +4908,7 @@
         <f>C31*C2/C11</f>
         <v>41.069999999999993</v>
       </c>
-      <c r="D18" s="32"/>
+      <c r="D18" s="31"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
@@ -4914,7 +4922,7 @@
         <f>C32*C2/C11</f>
         <v>33.950000000000003</v>
       </c>
-      <c r="F19" s="22"/>
+      <c r="F19" s="21"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
@@ -4948,11 +4956,11 @@
       <c r="A22" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="116">
+      <c r="B22" s="115">
         <f>'Estándar técnico'!B18</f>
         <v>0.83994289962825286</v>
       </c>
-      <c r="C22" s="116">
+      <c r="C22" s="115">
         <f>(C4*C2)/C14</f>
         <v>0.786536157779401</v>
       </c>
@@ -4962,11 +4970,11 @@
       <c r="A23" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="24">
         <f>'Estándar técnico'!B13</f>
         <v>0.92</v>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="24">
         <f>C5*C2/C15</f>
         <v>0.91523791352515771</v>
       </c>
@@ -5029,44 +5037,44 @@
       <c r="A28" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="25">
+      <c r="B28" s="24">
         <f>B27/B18</f>
         <v>0.16005710037174717</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="24">
         <f>C27/C18</f>
         <v>0.21346384222059878</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="78"/>
-      <c r="B29" s="79"/>
-      <c r="C29" s="79"/>
+      <c r="A29" s="77"/>
+      <c r="B29" s="78"/>
+      <c r="C29" s="78"/>
     </row>
     <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="109" t="s">
+      <c r="A30" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="B30" s="110" t="s">
+      <c r="B30" s="109" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="110" t="s">
+      <c r="C30" s="109" t="s">
         <v>4</v>
       </c>
-      <c r="D30" s="111" t="s">
+      <c r="D30" s="110" t="s">
         <v>92</v>
       </c>
-      <c r="E30" s="108" t="s">
+      <c r="E30" s="107" t="s">
         <v>91</v>
       </c>
-      <c r="F30" s="108" t="s">
+      <c r="F30" s="107" t="s">
         <v>93</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="75" t="s">
+      <c r="A31" s="74" t="s">
         <v>90</v>
       </c>
       <c r="B31" s="9">
@@ -5077,15 +5085,15 @@
         <f>C14/C2*1000</f>
         <v>323.69776962168265</v>
       </c>
-      <c r="D31" s="80">
+      <c r="D31" s="79">
         <f>(B31-C31)*C2/1000</f>
         <v>-1.4328186015831235</v>
       </c>
-      <c r="E31" s="80">
+      <c r="E31" s="79">
         <f>D31*B34</f>
         <v>-7.9478447829815853</v>
       </c>
-      <c r="F31" s="80">
+      <c r="F31" s="79">
         <f>E31/C2</f>
         <v>-1.2466034228906435E-2</v>
       </c>
@@ -5093,7 +5101,7 @@
       <c r="H31" s="1"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="40" t="s">
+      <c r="A32" s="39" t="s">
         <v>74</v>
       </c>
       <c r="B32" s="7">
@@ -5104,15 +5112,15 @@
         <f>C15/C2*1000</f>
         <v>267.58069828722006</v>
       </c>
-      <c r="D32" s="21">
+      <c r="D32" s="20">
         <f>(B32-C32)*C2/1000</f>
         <v>2.6512499999999521</v>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="20">
         <f>D32*B35</f>
         <v>26.215559999999527</v>
       </c>
-      <c r="F32" s="21">
+      <c r="F32" s="20">
         <f>E32/C2</f>
         <v>4.1118577075098077E-2</v>
       </c>
@@ -5120,17 +5128,17 @@
       <c r="H32" s="1"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="63" t="s">
+      <c r="A33" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="B33" s="53"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="48"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="47"/>
       <c r="E33" s="15">
         <f>SUM(E31:E32)</f>
         <v>18.267715217017944</v>
       </c>
-      <c r="F33" s="89">
+      <c r="F33" s="88">
         <f>SUM(F31:F32)</f>
         <v>2.8652542846191641E-2</v>
       </c>
@@ -5138,21 +5146,21 @@
       <c r="H33" s="1"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="75" t="s">
+      <c r="A34" s="74" t="s">
         <v>75</v>
       </c>
-      <c r="B34" s="125">
+      <c r="B34" s="124">
         <v>5.5469999999999997</v>
       </c>
-      <c r="C34" s="127">
+      <c r="C34" s="126">
         <v>5.6059999999999999</v>
       </c>
       <c r="D34" s="17"/>
-      <c r="E34" s="100">
+      <c r="E34" s="99">
         <f>(B34-C34)*C2</f>
         <v>-37.616040000000098</v>
       </c>
-      <c r="F34" s="80">
+      <c r="F34" s="79">
         <f>E34/C2</f>
         <v>-5.9000000000000156E-2</v>
       </c>
@@ -5160,21 +5168,21 @@
       <c r="H34" s="1"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="40" t="s">
+      <c r="A35" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="B35" s="126">
+      <c r="B35" s="125">
         <v>9.8879999999999999</v>
       </c>
-      <c r="C35" s="128">
+      <c r="C35" s="127">
         <v>9.7690000000000001</v>
       </c>
-      <c r="D35" s="82"/>
-      <c r="E35" s="101">
+      <c r="D35" s="81"/>
+      <c r="E35" s="100">
         <f>(B35-C35)*C2</f>
         <v>75.869639999999848</v>
       </c>
-      <c r="F35" s="21">
+      <c r="F35" s="20">
         <f>E35/C2</f>
         <v>0.11899999999999977</v>
       </c>
@@ -5182,17 +5190,17 @@
       <c r="H35" s="1"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="103" t="s">
+      <c r="A36" s="102" t="s">
         <v>89</v>
       </c>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
-      <c r="D36" s="102"/>
-      <c r="E36" s="89">
+      <c r="D36" s="101"/>
+      <c r="E36" s="88">
         <f>SUM(E34:E35)</f>
         <v>38.25359999999975</v>
       </c>
-      <c r="F36" s="89">
+      <c r="F36" s="88">
         <f>E36/C2</f>
         <v>5.9999999999999616E-2</v>
       </c>
@@ -5200,31 +5208,31 @@
       <c r="H36" s="1"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="78"/>
-      <c r="B37" s="78"/>
-      <c r="C37" s="78"/>
+      <c r="A37" s="77"/>
+      <c r="B37" s="77"/>
+      <c r="C37" s="77"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="81"/>
+      <c r="E37" s="80"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
     <row r="38" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="113" t="s">
+      <c r="A38" s="112" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="114" t="s">
+      <c r="B38" s="113" t="s">
         <v>40</v>
       </c>
-      <c r="C38" s="114" t="s">
+      <c r="C38" s="113" t="s">
         <v>4</v>
       </c>
-      <c r="D38" s="114" t="s">
+      <c r="D38" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="E38" s="115" t="s">
+      <c r="E38" s="114" t="s">
         <v>91</v>
       </c>
-      <c r="F38" s="108" t="s">
+      <c r="F38" s="107" t="s">
         <v>93</v>
       </c>
       <c r="G38" s="1"/>
@@ -5250,7 +5258,7 @@
         <f>D39*B34</f>
         <v>-7.9478447829814991</v>
       </c>
-      <c r="F39" s="80">
+      <c r="F39" s="79">
         <f>E39/C2</f>
         <v>-1.2466034228906299E-2</v>
       </c>
@@ -5258,26 +5266,26 @@
       <c r="H39" s="1"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="82" t="s">
+      <c r="A40" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="B40" s="21">
+      <c r="B40" s="20">
         <f>B15</f>
         <v>173.24999999999997</v>
       </c>
-      <c r="C40" s="21">
+      <c r="C40" s="20">
         <f>C15</f>
         <v>170.59875</v>
       </c>
-      <c r="D40" s="21">
+      <c r="D40" s="20">
         <f>B40-C40</f>
         <v>2.6512499999999761</v>
       </c>
-      <c r="E40" s="21">
+      <c r="E40" s="20">
         <f>D40*B35</f>
         <v>26.215559999999762</v>
       </c>
-      <c r="F40" s="21">
+      <c r="F40" s="20">
         <f>E40/C2</f>
         <v>4.1118577075098445E-2</v>
       </c>
@@ -5285,14 +5293,14 @@
       <c r="H40" s="1"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="48"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="89">
+      <c r="B41" s="47"/>
+      <c r="C41" s="47"/>
+      <c r="D41" s="47"/>
+      <c r="E41" s="88">
         <f>SUM(E39:E40)</f>
         <v>18.267715217018264</v>
       </c>
-      <c r="F41" s="89">
+      <c r="F41" s="88">
         <f>SUM(F39:F40)</f>
         <v>2.8652542846192147E-2</v>
       </c>
@@ -5300,37 +5308,37 @@
       <c r="H41" s="1"/>
     </row>
     <row r="43" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="112" t="s">
+      <c r="A43" s="111" t="s">
         <v>82</v>
       </c>
-      <c r="B43" s="51" t="s">
+      <c r="B43" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="C43" s="51" t="s">
+      <c r="C43" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="D43" s="51" t="s">
+      <c r="D43" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="E43" s="108" t="s">
+      <c r="E43" s="107" t="s">
         <v>91</v>
       </c>
-      <c r="F43" s="115" t="s">
+      <c r="F43" s="114" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="91" t="s">
+      <c r="A44" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="B44" s="80"/>
-      <c r="C44" s="80"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="80"/>
+      <c r="B44" s="79"/>
+      <c r="C44" s="79"/>
+      <c r="D44" s="91"/>
+      <c r="E44" s="79"/>
       <c r="F44" s="17"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="34" t="s">
+      <c r="A45" s="33" t="s">
         <v>38</v>
       </c>
       <c r="B45" s="15">
@@ -5355,14 +5363,14 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="50" t="s">
+      <c r="A46" s="49" t="s">
         <v>31</v>
       </c>
       <c r="B46" s="15">
         <f>B$4/B$22*C$2</f>
         <v>204.94393139841688</v>
       </c>
-      <c r="C46" s="85">
+      <c r="C46" s="84">
         <f>(B$4/C$22)*C$2</f>
         <v>218.85986842105262</v>
       </c>
@@ -5380,7 +5388,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="83" t="s">
+      <c r="A47" s="82" t="s">
         <v>43</v>
       </c>
       <c r="B47" s="15"/>
@@ -5399,36 +5407,36 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="84" t="s">
+      <c r="A48" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="B48" s="86"/>
-      <c r="C48" s="86"/>
-      <c r="D48" s="86">
+      <c r="B48" s="85"/>
+      <c r="C48" s="85"/>
+      <c r="D48" s="85">
         <f>SUM(D45:D47)</f>
         <v>-1.7021723810176623</v>
       </c>
-      <c r="E48" s="86">
+      <c r="E48" s="85">
         <f>SUM(E45:E47)</f>
         <v>-9.4419501975049798</v>
       </c>
-      <c r="F48" s="21">
+      <c r="F48" s="20">
         <f t="shared" si="0"/>
         <v>-1.4809508434508093E-2</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="91" t="s">
+      <c r="A49" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="B49" s="80"/>
-      <c r="C49" s="80"/>
-      <c r="D49" s="92"/>
-      <c r="E49" s="80"/>
+      <c r="B49" s="79"/>
+      <c r="C49" s="79"/>
+      <c r="D49" s="91"/>
+      <c r="E49" s="79"/>
       <c r="F49" s="15"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="34" t="s">
+      <c r="A50" s="33" t="s">
         <v>39</v>
       </c>
       <c r="B50" s="15">
@@ -5439,7 +5447,7 @@
         <f>C2*C5/B23</f>
         <v>169.7157</v>
       </c>
-      <c r="D50" s="87">
+      <c r="D50" s="86">
         <f>B50-C50</f>
         <v>3.5342999999999734</v>
       </c>
@@ -5453,7 +5461,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="34" t="s">
+      <c r="A51" s="33" t="s">
         <v>32</v>
       </c>
       <c r="B51" s="15">
@@ -5464,7 +5472,7 @@
         <f>C2*B5/C23</f>
         <v>174.1514393630053</v>
       </c>
-      <c r="D51" s="87">
+      <c r="D51" s="86">
         <f>B51-C51</f>
         <v>-0.90143936300532346</v>
       </c>
@@ -5478,11 +5486,11 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="83" t="s">
+      <c r="A52" s="82" t="s">
         <v>43</v>
       </c>
       <c r="B52" s="15"/>
-      <c r="C52" s="48"/>
+      <c r="C52" s="47"/>
       <c r="D52" s="15">
         <f>(B23-C23)*(B5-C5)*C2</f>
         <v>1.5484190849792408E-2</v>
@@ -5497,16 +5505,16 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="90" t="s">
+      <c r="A53" s="89" t="s">
         <v>80</v>
       </c>
-      <c r="B53" s="21"/>
-      <c r="C53" s="88"/>
-      <c r="D53" s="21">
+      <c r="B53" s="20"/>
+      <c r="C53" s="87"/>
+      <c r="D53" s="20">
         <f>SUM(D50:D52)</f>
         <v>2.6483448278444421</v>
       </c>
-      <c r="E53" s="21">
+      <c r="E53" s="20">
         <f>SUM(E50:E52)</f>
         <v>26.186833657725845</v>
       </c>
@@ -5516,29 +5524,29 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="97" t="s">
+      <c r="A54" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B54" s="57"/>
-      <c r="C54" s="98"/>
-      <c r="D54" s="99"/>
-      <c r="E54" s="57">
+      <c r="B54" s="56"/>
+      <c r="C54" s="97"/>
+      <c r="D54" s="98"/>
+      <c r="E54" s="56">
         <f>E53+E48</f>
         <v>16.744883460220866</v>
       </c>
-      <c r="F54" s="57">
+      <c r="F54" s="56">
         <f>F53+F48</f>
         <v>2.6264011952162727E-2</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="49" t="s">
+      <c r="A55" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="B55" s="93"/>
-      <c r="C55" s="93"/>
-      <c r="D55" s="93"/>
-      <c r="E55" s="80">
+      <c r="B55" s="92"/>
+      <c r="C55" s="92"/>
+      <c r="D55" s="92"/>
+      <c r="E55" s="79">
         <f>SUM(E45,E50)</f>
         <v>99.788230277748355</v>
       </c>
@@ -5548,7 +5556,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="27" t="s">
+      <c r="A56" s="26" t="s">
         <v>84</v>
       </c>
       <c r="E56" s="15">
@@ -5561,7 +5569,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="27" t="s">
+      <c r="A57" s="26" t="s">
         <v>43</v>
       </c>
       <c r="D57" s="1"/>
@@ -5569,23 +5577,23 @@
         <f>SUM(E47+E52)</f>
         <v>3.0617882684296309</v>
       </c>
-      <c r="F57" s="21">
+      <c r="F57" s="20">
         <f t="shared" si="0"/>
         <v>4.8023531407704861E-3</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="94" t="s">
+      <c r="A58" s="93" t="s">
         <v>83</v>
       </c>
-      <c r="B58" s="95"/>
-      <c r="C58" s="95"/>
-      <c r="D58" s="95"/>
-      <c r="E58" s="96">
+      <c r="B58" s="94"/>
+      <c r="C58" s="94"/>
+      <c r="D58" s="94"/>
+      <c r="E58" s="95">
         <f>1-ABS(E57/E54)</f>
         <v>0.81715081650444366</v>
       </c>
-      <c r="F58" s="96"/>
+      <c r="F58" s="95"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C61" s="1"/>
